--- a/fixtures/invoice-extras.xlsx
+++ b/fixtures/invoice-extras.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Invoice" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Invoice!$A$1:$D$9</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
